--- a/backtest_runs/20260410_193731/by_symbol/UCAPM/UCAPM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/UCAPM/UCAPM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>119480.5</v>
@@ -771,7 +771,7 @@
         <v>-1082.249999999996</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>118398.25</v>
@@ -817,7 +817,7 @@
         <v>-1298.699999999992</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>117099.55</v>
@@ -909,7 +909,7 @@
         <v>-4329.000000000004</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>114718.6</v>
@@ -1185,7 +1185,7 @@
         <v>-9523.799999999988</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>109090.9</v>
@@ -1231,7 +1231,7 @@
         <v>-216.4500000000146</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>108874.45</v>
@@ -1277,7 +1277,7 @@
         <v>-3246.749999999989</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>105627.7</v>
@@ -1323,7 +1323,7 @@
         <v>-1731.600000000002</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>103896.1</v>
@@ -1415,7 +1415,7 @@
         <v>-1948.049999999997</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>102813.85</v>
